--- a/nr-doc-core-body-structure/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/nr-doc-core-body-structure/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:03:50+00:00</t>
+    <t>2026-09-17T13:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
